--- a/pic/systemflow.xlsx
+++ b/pic/systemflow.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\work\ClickSendSkill-main\pic\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1066B432-0831-485B-9B09-664A3246F2AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36559195-2421-4D37-BF1B-CEA9716606B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="150" yWindow="585" windowWidth="25035" windowHeight="10815" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6750" yWindow="2625" windowWidth="21435" windowHeight="11505" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="flow" sheetId="1" r:id="rId1"/>
@@ -85,13 +85,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>8</xdr:col>
+      <xdr:col>10</xdr:col>
       <xdr:colOff>504826</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>9526</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
+      <xdr:col>11</xdr:col>
       <xdr:colOff>481466</xdr:colOff>
       <xdr:row>3</xdr:row>
       <xdr:rowOff>171450</xdr:rowOff>
@@ -135,16 +135,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>147812</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>49996</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>292517</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>33335</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>85725</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>218046</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>581025</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>37831</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
@@ -159,10 +159,10 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="9063212" y="2669371"/>
-          <a:ext cx="1995313" cy="1834925"/>
-          <a:chOff x="6148562" y="2774146"/>
-          <a:chExt cx="1995313" cy="1834925"/>
+          <a:off x="7801392" y="3128960"/>
+          <a:ext cx="1653758" cy="1433246"/>
+          <a:chOff x="6074188" y="2857500"/>
+          <a:chExt cx="1660108" cy="1433246"/>
         </a:xfrm>
       </xdr:grpSpPr>
       <xdr:pic>
@@ -192,8 +192,8 @@
         </xdr:blipFill>
         <xdr:spPr>
           <a:xfrm rot="20021890">
-            <a:off x="6148562" y="2774146"/>
-            <a:ext cx="1512265" cy="1834925"/>
+            <a:off x="6074188" y="2862508"/>
+            <a:ext cx="1208451" cy="1428238"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -227,7 +227,7 @@
         </xdr:blipFill>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="6429376" y="3228976"/>
+            <a:off x="6305551" y="3228976"/>
             <a:ext cx="628650" cy="628650"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
@@ -248,7 +248,7 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm rot="2202049" flipH="1">
-            <a:off x="7648573" y="2933699"/>
+            <a:off x="7277098" y="2857500"/>
             <a:ext cx="323851" cy="542925"/>
           </a:xfrm>
           <a:prstGeom prst="lightningBolt">
@@ -296,7 +296,7 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm rot="7102652">
-            <a:off x="7638899" y="3543529"/>
+            <a:off x="7324574" y="3372077"/>
             <a:ext cx="178129" cy="627668"/>
           </a:xfrm>
           <a:prstGeom prst="lightningBolt">
@@ -358,8 +358,8 @@
         </xdr:blipFill>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="7691707" y="3279903"/>
-            <a:ext cx="452168" cy="466754"/>
+            <a:off x="7377382" y="3251328"/>
+            <a:ext cx="356914" cy="368427"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -379,13 +379,15 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="6362700" y="3743325"/>
-            <a:ext cx="812613" cy="264560"/>
+            <a:off x="6343651" y="3824290"/>
+            <a:ext cx="628646" cy="161925"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
           </a:prstGeom>
-          <a:noFill/>
+          <a:solidFill>
+            <a:schemeClr val="bg1"/>
+          </a:solidFill>
         </xdr:spPr>
         <xdr:style>
           <a:lnRef idx="0">
@@ -402,8 +404,8 @@
           </a:fontRef>
         </xdr:style>
         <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t">
-            <a:spAutoFit/>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+            <a:noAutofit/>
           </a:bodyPr>
           <a:lstStyle/>
           <a:p>
@@ -420,16 +422,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>152400</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>180975</xdr:rowOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>373855</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>159542</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>542925</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>235985</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>561973</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>28573</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
@@ -444,10 +446,10 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="7010400" y="3038475"/>
-          <a:ext cx="1076325" cy="1007510"/>
+          <a:off x="6517480" y="3493292"/>
+          <a:ext cx="870743" cy="821531"/>
           <a:chOff x="3686175" y="2990850"/>
-          <a:chExt cx="1076325" cy="1007510"/>
+          <a:chExt cx="1312320" cy="1056186"/>
         </a:xfrm>
       </xdr:grpSpPr>
       <xdr:pic>
@@ -498,8 +500,8 @@
         </xdr:nvSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="3838575" y="3733800"/>
-            <a:ext cx="812613" cy="264560"/>
+            <a:off x="3738452" y="3770538"/>
+            <a:ext cx="1260043" cy="276498"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -539,16 +541,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>542925</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>115822</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>404818</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>3057</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>542925</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>115822</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>404818</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>3057</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -566,7 +568,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8086725" y="3449572"/>
+          <a:off x="7262818" y="3813057"/>
           <a:ext cx="0" cy="0"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
@@ -595,16 +597,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>542925</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>104776</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>404818</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>3057</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>428626</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>115822</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>523880</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>4761</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -621,9 +623,9 @@
         </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm flipV="1">
-          <a:off x="8086725" y="3438526"/>
-          <a:ext cx="1257301" cy="11046"/>
+        <a:xfrm>
+          <a:off x="7262818" y="3813057"/>
+          <a:ext cx="804862" cy="1704"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -653,6 +655,1025 @@
         </a:fontRef>
       </xdr:style>
     </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>659607</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>461963</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>69056</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="テキスト ボックス 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D0A11D34-3B01-4F4C-905D-B24B72942863}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7517607" y="3581400"/>
+          <a:ext cx="488156" cy="297656"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" b="1"/>
+            <a:t>SMS</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="1"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>261983</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>168306</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>366015</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>143919</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="図 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0AF3BEEA-ADDF-4E6E-A820-E6D589381EE2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm rot="19967568">
+          <a:off x="1633583" y="2549556"/>
+          <a:ext cx="789832" cy="689988"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>563117</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>23814</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>104774</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>66676</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="26" name="グループ化 25">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BBC71A13-506D-AC94-1C28-636C0F599F6E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="2610992" y="3595689"/>
+          <a:ext cx="906907" cy="757237"/>
+          <a:chOff x="3007180" y="3262313"/>
+          <a:chExt cx="1354829" cy="1009647"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="10" name="図 9">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C2FF24B5-7F02-CB1A-B1CD-40E803E7CAEA}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7" cstate="print">
+            <a:extLst>
+              <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+                <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+              </a:ext>
+            </a:extLst>
+          </a:blip>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="3143251" y="3262313"/>
+            <a:ext cx="911700" cy="547688"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="14" name="テキスト ボックス 13">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{27CEA0C2-AAFB-43B0-AB7E-A62AE2170676}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr txBox="1"/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="3007180" y="3936205"/>
+            <a:ext cx="1354829" cy="335755"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t">
+            <a:noAutofit/>
+          </a:bodyPr>
+          <a:lstStyle/>
+          <a:p>
+            <a:r>
+              <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" b="1"/>
+              <a:t>Echo Device</a:t>
+            </a:r>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="1"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>360136</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>83349</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>73820</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>4766</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="30" name="グループ化 29">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0F8F4415-1CDB-1EE9-C086-DD40F7CCCB98}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="3773261" y="3417099"/>
+          <a:ext cx="1078934" cy="873917"/>
+          <a:chOff x="2561329" y="3048001"/>
+          <a:chExt cx="1436942" cy="1117283"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="20" name="図 19">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{639A35B2-9C94-0FA2-7D3D-E253C7350DDD}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8" cstate="print">
+            <a:extLst>
+              <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+                <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+              </a:ext>
+            </a:extLst>
+          </a:blip>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="2607470" y="3048001"/>
+            <a:ext cx="1000124" cy="1000124"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="27" name="テキスト ボックス 26">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{86B169BB-CE32-4680-B529-416B23B539AB}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr txBox="1"/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="2561329" y="3928519"/>
+            <a:ext cx="1436942" cy="236765"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t">
+            <a:noAutofit/>
+          </a:bodyPr>
+          <a:lstStyle/>
+          <a:p>
+            <a:r>
+              <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" b="1"/>
+              <a:t>Alexa</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" b="1" baseline="0"/>
+              <a:t> Cloud</a:t>
+            </a:r>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="1"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>121445</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>140905</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>628650</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>92875</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="29" name="グループ化 28">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A689BC33-9A9C-40EC-3AA7-7E39BB22FF1A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="4899820" y="3474655"/>
+          <a:ext cx="1189830" cy="904470"/>
+          <a:chOff x="4180773" y="3123752"/>
+          <a:chExt cx="1575148" cy="1143115"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="25" name="図 24">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7D82E37F-65A3-4EE7-C1EB-CB81FF3723F4}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9" cstate="print">
+            <a:extLst>
+              <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+                <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+              </a:ext>
+            </a:extLst>
+          </a:blip>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="4410284" y="3123752"/>
+            <a:ext cx="852278" cy="852277"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="28" name="テキスト ボックス 27">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{724B203C-2C7F-455B-AA9F-1AB82E1BBC1B}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr txBox="1"/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="4180773" y="3920768"/>
+            <a:ext cx="1575148" cy="346099"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t">
+            <a:noAutofit/>
+          </a:bodyPr>
+          <a:lstStyle/>
+          <a:p>
+            <a:r>
+              <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" b="1"/>
+              <a:t>Alexa-hosted</a:t>
+            </a:r>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="1"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>583597</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>229196</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>394985</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>236361</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="31" name="直線コネクタ 30">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0BD8F87C-7A8C-41B1-A56E-F6A91BB7F4C1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="10" idx="3"/>
+          <a:endCxn id="20" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3326797" y="3801071"/>
+          <a:ext cx="497188" cy="7165"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="28575">
+          <a:solidFill>
+            <a:schemeClr val="bg2">
+              <a:lumMod val="75000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:headEnd type="none" w="med" len="med"/>
+          <a:tailEnd type="triangle" w="med" len="med"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>464552</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>236361</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>295275</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>1830</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="32" name="直線コネクタ 31">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A2BD768F-9EA0-401D-A3DE-830A2D63EAB7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="20" idx="3"/>
+          <a:endCxn id="25" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4579352" y="3808236"/>
+          <a:ext cx="516523" cy="3594"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="28575">
+          <a:solidFill>
+            <a:schemeClr val="bg2">
+              <a:lumMod val="75000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:headEnd type="none" w="med" len="med"/>
+          <a:tailEnd type="triangle" w="med" len="med"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>254984</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>1830</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>373856</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>3057</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="33" name="直線コネクタ 32">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DB7A2B63-B489-49D9-8D9D-4F8B92026503}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="25" idx="3"/>
+          <a:endCxn id="15" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5741384" y="3811830"/>
+          <a:ext cx="804672" cy="1227"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="28575">
+          <a:solidFill>
+            <a:schemeClr val="bg2">
+              <a:lumMod val="75000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:headEnd type="none" w="med" len="med"/>
+          <a:tailEnd type="triangle" w="med" len="med"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>285750</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>226219</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>400049</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="40" name="テキスト ボックス 39">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7141C2A1-FEF7-45C5-B332-DE2D0AD92010}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5772150" y="3559969"/>
+          <a:ext cx="800099" cy="297656"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" b="1"/>
+            <a:t>REST</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" b="1" baseline="0"/>
+            <a:t> API</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="1"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>147636</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>16669</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>533400</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>183356</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="46" name="フリーフォーム: 図形 45">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9BF31A83-CC24-AA06-E433-C8BB7045807D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2205036" y="2874169"/>
+          <a:ext cx="5872164" cy="642937"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst>
+            <a:gd name="csX0" fmla="*/ 0 w 5917407"/>
+            <a:gd name="csY0" fmla="*/ 0 h 642937"/>
+            <a:gd name="csX1" fmla="*/ 4988719 w 5917407"/>
+            <a:gd name="csY1" fmla="*/ 0 h 642937"/>
+            <a:gd name="csX2" fmla="*/ 5917407 w 5917407"/>
+            <a:gd name="csY2" fmla="*/ 642937 h 642937"/>
+          </a:gdLst>
+          <a:ahLst/>
+          <a:cxnLst>
+            <a:cxn ang="0">
+              <a:pos x="csX0" y="csY0"/>
+            </a:cxn>
+            <a:cxn ang="0">
+              <a:pos x="csX1" y="csY1"/>
+            </a:cxn>
+            <a:cxn ang="0">
+              <a:pos x="csX2" y="csY2"/>
+            </a:cxn>
+          </a:cxnLst>
+          <a:rect l="l" t="t" r="r" b="b"/>
+          <a:pathLst>
+            <a:path w="5917407" h="642937">
+              <a:moveTo>
+                <a:pt x="0" y="0"/>
+              </a:moveTo>
+              <a:lnTo>
+                <a:pt x="4988719" y="0"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="5917407" y="642937"/>
+              </a:lnTo>
+            </a:path>
+          </a:pathLst>
+        </a:custGeom>
+        <a:noFill/>
+        <a:ln w="28575">
+          <a:solidFill>
+            <a:schemeClr val="bg2">
+              <a:lumMod val="75000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>316706</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>11906</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>71437</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="47" name="テキスト ボックス 46">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FFE13683-DD1D-4880-96FE-1603E14502FE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2374106" y="2631281"/>
+          <a:ext cx="483394" cy="297656"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" b="1"/>
+            <a:t>SMS</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="1"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>78581</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>210242</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>483392</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="51" name="グループ化 50">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{50705E4A-A150-0E44-45AF-C8484096D29C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="1443831" y="3305867"/>
+          <a:ext cx="1087436" cy="1085158"/>
+          <a:chOff x="1083469" y="3146323"/>
+          <a:chExt cx="1095374" cy="1085158"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="49" name="図 48">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B6AE6366-22C0-3D43-FD02-FC09F97388B6}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10">
+            <a:extLst>
+              <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+                <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+              </a:ext>
+            </a:extLst>
+          </a:blip>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="1309688" y="3146323"/>
+            <a:ext cx="809625" cy="809625"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="50" name="テキスト ボックス 49">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7256016D-7F05-43E1-B653-5F6C9A29D867}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr txBox="1"/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="1083469" y="3933825"/>
+            <a:ext cx="1095374" cy="297656"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t">
+            <a:noAutofit/>
+          </a:bodyPr>
+          <a:lstStyle/>
+          <a:p>
+            <a:r>
+              <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" b="1"/>
+              <a:t>Voice</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" b="1" baseline="0"/>
+              <a:t> Request</a:t>
+            </a:r>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="1"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+    </xdr:grpSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>

--- a/pic/systemflow.xlsx
+++ b/pic/systemflow.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\work\ClickSendSkill-main\pic\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\work\Alexa_skill\ClickSendSkill\pic\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36559195-2421-4D37-BF1B-CEA9716606B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{746CF137-F910-4245-8478-7114094BED78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6750" yWindow="2625" windowWidth="21435" windowHeight="11505" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1365" yWindow="690" windowWidth="26025" windowHeight="15075" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="flow" sheetId="1" r:id="rId1"/>
@@ -1676,6 +1676,228 @@
     </xdr:grpSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>39687</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>74901</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>515936</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>99218</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="23" name="グループ化 22">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5053FB44-A0CC-4FB7-D54E-47A4B39A6C8F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="1404937" y="4361151"/>
+          <a:ext cx="1158874" cy="976817"/>
+          <a:chOff x="4937125" y="4972339"/>
+          <a:chExt cx="1158874" cy="976817"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="6" name="テキスト ボックス 5">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{687B13F1-0174-442B-94C1-95FB0624978B}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr txBox="1"/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="4992686" y="5651500"/>
+            <a:ext cx="1103313" cy="297656"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t">
+            <a:noAutofit/>
+          </a:bodyPr>
+          <a:lstStyle/>
+          <a:p>
+            <a:r>
+              <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100" b="1"/>
+              <a:t>Web Browser</a:t>
+            </a:r>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100" b="1"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="22" name="図 21">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{68FBC410-F409-C4F8-910E-CC4880FADA09}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11" cstate="print">
+            <a:extLst>
+              <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+                <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+              </a:ext>
+            </a:extLst>
+          </a:blip>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="4937125" y="4972339"/>
+            <a:ext cx="1039813" cy="764340"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>396876</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>79375</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>373064</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="36" name="フリーフォーム: 図形 35">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{186CFDD7-61F8-46D9-99C6-7437B72873A2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="2444751" y="4127500"/>
+          <a:ext cx="4071938" cy="635000"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst>
+            <a:gd name="csX0" fmla="*/ 0 w 5917407"/>
+            <a:gd name="csY0" fmla="*/ 0 h 642937"/>
+            <a:gd name="csX1" fmla="*/ 4988719 w 5917407"/>
+            <a:gd name="csY1" fmla="*/ 0 h 642937"/>
+            <a:gd name="csX2" fmla="*/ 5917407 w 5917407"/>
+            <a:gd name="csY2" fmla="*/ 642937 h 642937"/>
+          </a:gdLst>
+          <a:ahLst/>
+          <a:cxnLst>
+            <a:cxn ang="0">
+              <a:pos x="csX0" y="csY0"/>
+            </a:cxn>
+            <a:cxn ang="0">
+              <a:pos x="csX1" y="csY1"/>
+            </a:cxn>
+            <a:cxn ang="0">
+              <a:pos x="csX2" y="csY2"/>
+            </a:cxn>
+          </a:cxnLst>
+          <a:rect l="l" t="t" r="r" b="b"/>
+          <a:pathLst>
+            <a:path w="5917407" h="642937">
+              <a:moveTo>
+                <a:pt x="0" y="0"/>
+              </a:moveTo>
+              <a:lnTo>
+                <a:pt x="4988719" y="0"/>
+              </a:lnTo>
+              <a:lnTo>
+                <a:pt x="5917407" y="642937"/>
+              </a:lnTo>
+            </a:path>
+          </a:pathLst>
+        </a:custGeom>
+        <a:noFill/>
+        <a:ln w="28575">
+          <a:solidFill>
+            <a:schemeClr val="bg2">
+              <a:lumMod val="75000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
